--- a/GRAMMAR/10_17_12.xlsx
+++ b/GRAMMAR/10_17_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561AD893-05A3-4C5D-A7CA-529DF52E9A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932D2BA6-613C-41A7-BB5E-08D44DC2D748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19140" yWindow="1005" windowWidth="19260" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18720" yWindow="675" windowWidth="19260" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>Fre</t>
   </si>
@@ -377,9 +377,6 @@
   </si>
   <si>
     <t>光滑；顺利；流畅</t>
-  </si>
-  <si>
-    <t>光滑；顺利；流畅</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -397,13 +394,19 @@
   <si>
     <t>好像</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>含义</t>
+  </si>
+  <si>
+    <t>History</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,14 +416,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -442,9 +437,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFBDB7AE"/>
-      <name val="黑体"/>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -484,18 +479,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -798,498 +792,501 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="36.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9" style="2" customWidth="1"/>
-    <col min="5" max="5" width="27.875" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A3" s="1">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A4" s="1">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A5" s="1">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A6" s="1">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A7" s="1">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A8" s="1">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A9" s="1">
+        <v>0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A10" s="1">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A11" s="1">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A12" s="1">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A13" s="1">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A14" s="1">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A15" s="1">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A16" s="1">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17" s="1">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18" s="1">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="1">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20" s="1">
+        <v>0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A21" s="1">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A22" s="1">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23" s="1">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A24" s="1">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25" s="1">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A26" s="1">
+        <v>0</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
+        <v>0</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28" s="1">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30" s="1">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A31" s="1">
+        <v>1</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A32" s="1">
+        <v>1</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A33" s="1">
+        <v>1</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A34" s="1">
+        <v>1</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A35" s="1">
+        <v>1</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A36" s="1">
+        <v>1</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A37" s="1">
+        <v>1</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A38" s="1">
+        <v>1</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A39" s="1">
+        <v>1</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A40" s="1">
+        <v>1</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" s="2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" s="2">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4" s="2">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A5" s="2">
-        <v>0</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A6" s="2">
-        <v>0</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A7" s="2">
-        <v>0</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A8" s="2">
-        <v>0</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9" s="2">
-        <v>0</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A10" s="2">
-        <v>0</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A11" s="2">
-        <v>0</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A12" s="2">
-        <v>0</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A13" s="2">
-        <v>0</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A14" s="2">
-        <v>0</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A15" s="2">
-        <v>0</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A16" s="2">
-        <v>0</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17" s="2">
-        <v>0</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="2">
-        <v>0</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19" s="2">
-        <v>0</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20" s="2">
-        <v>0</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21" s="2">
-        <v>0</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22" s="2">
-        <v>0</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23" s="2">
-        <v>0</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24" s="2">
-        <v>0</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25" s="2">
-        <v>0</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26" s="2">
-        <v>0</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27" s="2">
-        <v>0</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28" s="2">
-        <v>0</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A29" s="2">
-        <v>0</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A30" s="2">
-        <v>0</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A31" s="2">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A41" s="1">
         <v>1</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A32" s="2">
+      <c r="B41" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A42" s="1">
         <v>1</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A33" s="2">
-        <v>1</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A34" s="2">
-        <v>1</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A35" s="2">
-        <v>1</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A36" s="2">
-        <v>1</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A37" s="2">
-        <v>1</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A38" s="2">
-        <v>1</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A39" s="2">
-        <v>1</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A40" s="2">
-        <v>1</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A41" s="2">
-        <v>1</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A42" s="2">
-        <v>1</v>
-      </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
